--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S468"/>
+  <dimension ref="A1:S471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29944,6 +29944,195 @@
         <v>259.36</v>
       </c>
       <c r="S468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>238.07</v>
+      </c>
+      <c r="C469" t="n">
+        <v>237.39</v>
+      </c>
+      <c r="D469" t="n">
+        <v>249.17</v>
+      </c>
+      <c r="E469" t="n">
+        <v>246.1</v>
+      </c>
+      <c r="F469" t="n">
+        <v>245.92</v>
+      </c>
+      <c r="G469" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="H469" t="n">
+        <v>248.72</v>
+      </c>
+      <c r="I469" t="n">
+        <v>250.76</v>
+      </c>
+      <c r="J469" t="n">
+        <v>256.19</v>
+      </c>
+      <c r="K469" t="n">
+        <v>254.69</v>
+      </c>
+      <c r="L469" t="n">
+        <v>257.01</v>
+      </c>
+      <c r="M469" t="n">
+        <v>254.67</v>
+      </c>
+      <c r="N469" t="n">
+        <v>253.99</v>
+      </c>
+      <c r="O469" t="n">
+        <v>253.45</v>
+      </c>
+      <c r="P469" t="n">
+        <v>251.31</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>255.78</v>
+      </c>
+      <c r="R469" t="n">
+        <v>257.2</v>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>238.42</v>
+      </c>
+      <c r="C470" t="n">
+        <v>237.83</v>
+      </c>
+      <c r="D470" t="n">
+        <v>249.55</v>
+      </c>
+      <c r="E470" t="n">
+        <v>246.41</v>
+      </c>
+      <c r="F470" t="n">
+        <v>246.73</v>
+      </c>
+      <c r="G470" t="n">
+        <v>248.63</v>
+      </c>
+      <c r="H470" t="n">
+        <v>248.85</v>
+      </c>
+      <c r="I470" t="n">
+        <v>250.74</v>
+      </c>
+      <c r="J470" t="n">
+        <v>256.59</v>
+      </c>
+      <c r="K470" t="n">
+        <v>254.65</v>
+      </c>
+      <c r="L470" t="n">
+        <v>257.16</v>
+      </c>
+      <c r="M470" t="n">
+        <v>254.35</v>
+      </c>
+      <c r="N470" t="n">
+        <v>253.85</v>
+      </c>
+      <c r="O470" t="n">
+        <v>253.96</v>
+      </c>
+      <c r="P470" t="n">
+        <v>251.8</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>255.48</v>
+      </c>
+      <c r="R470" t="n">
+        <v>256.76</v>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>239.65</v>
+      </c>
+      <c r="C471" t="n">
+        <v>239.25</v>
+      </c>
+      <c r="D471" t="n">
+        <v>251.03</v>
+      </c>
+      <c r="E471" t="n">
+        <v>248.02</v>
+      </c>
+      <c r="F471" t="n">
+        <v>248.14</v>
+      </c>
+      <c r="G471" t="n">
+        <v>249.71</v>
+      </c>
+      <c r="H471" t="n">
+        <v>248.69</v>
+      </c>
+      <c r="I471" t="n">
+        <v>251.23</v>
+      </c>
+      <c r="J471" t="n">
+        <v>257.44</v>
+      </c>
+      <c r="K471" t="n">
+        <v>255.32</v>
+      </c>
+      <c r="L471" t="n">
+        <v>257.62</v>
+      </c>
+      <c r="M471" t="n">
+        <v>255.53</v>
+      </c>
+      <c r="N471" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="O471" t="n">
+        <v>256.33</v>
+      </c>
+      <c r="P471" t="n">
+        <v>253.23</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>255.9</v>
+      </c>
+      <c r="R471" t="n">
+        <v>256.89</v>
+      </c>
+      <c r="S471" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29960,7 +30149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B469"/>
+  <dimension ref="A1:B472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34653,6 +34842,36 @@
       </c>
       <c r="B469" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -34815,28 +35034,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1670975256543808</v>
+        <v>0.1685143509279862</v>
       </c>
       <c r="J2" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K2" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0876684142575519</v>
+        <v>0.09013926774685566</v>
       </c>
       <c r="M2" t="n">
-        <v>3.307392084005057</v>
+        <v>3.294188987100456</v>
       </c>
       <c r="N2" t="n">
-        <v>16.72162556801621</v>
+        <v>16.62584034578931</v>
       </c>
       <c r="O2" t="n">
-        <v>4.089208428047684</v>
+        <v>4.077479656085278</v>
       </c>
       <c r="P2" t="n">
-        <v>233.059137153872</v>
+        <v>233.0441159231337</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34887,28 +35106,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04046844431098749</v>
+        <v>0.04167293546139676</v>
       </c>
       <c r="J3" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K3" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006038685017917933</v>
+        <v>0.006488507338268223</v>
       </c>
       <c r="M3" t="n">
-        <v>3.28517319483859</v>
+        <v>3.271123036851405</v>
       </c>
       <c r="N3" t="n">
-        <v>15.51275811585361</v>
+        <v>15.42358060488464</v>
       </c>
       <c r="O3" t="n">
-        <v>3.938623886061427</v>
+        <v>3.927286672103863</v>
       </c>
       <c r="P3" t="n">
-        <v>236.098036534058</v>
+        <v>236.0852630492197</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34959,28 +35178,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002425053447002487</v>
+        <v>0.00307981573271992</v>
       </c>
       <c r="J4" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K4" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L4" t="n">
-        <v>2.06467314634029e-05</v>
+        <v>3.376744924754593e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.372577981595226</v>
+        <v>3.355550523521987</v>
       </c>
       <c r="N4" t="n">
-        <v>16.39121889331318</v>
+        <v>16.29241525654031</v>
       </c>
       <c r="O4" t="n">
-        <v>4.048607031228541</v>
+        <v>4.036386410707022</v>
       </c>
       <c r="P4" t="n">
-        <v>249.3258839494603</v>
+        <v>249.3189346359805</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35031,28 +35250,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03631363304460879</v>
+        <v>-0.03544817071878493</v>
       </c>
       <c r="J5" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K5" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004644266987105183</v>
+        <v>0.004487787316071801</v>
       </c>
       <c r="M5" t="n">
-        <v>3.268245115933281</v>
+        <v>3.252309521204915</v>
       </c>
       <c r="N5" t="n">
-        <v>16.26407775976922</v>
+        <v>16.16779925049262</v>
       </c>
       <c r="O5" t="n">
-        <v>4.032874627330885</v>
+        <v>4.020920199468353</v>
       </c>
       <c r="P5" t="n">
-        <v>247.1351310876967</v>
+        <v>247.1259489243954</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35103,28 +35322,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08743921058018247</v>
+        <v>-0.08455237795812463</v>
       </c>
       <c r="J6" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K6" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02534327868635489</v>
+        <v>0.02401536293709117</v>
       </c>
       <c r="M6" t="n">
-        <v>3.321087533831431</v>
+        <v>3.315682856025467</v>
       </c>
       <c r="N6" t="n">
-        <v>16.92116403836365</v>
+        <v>16.85211464782152</v>
       </c>
       <c r="O6" t="n">
-        <v>4.113534251512153</v>
+        <v>4.105132719879045</v>
       </c>
       <c r="P6" t="n">
-        <v>246.977575320634</v>
+        <v>246.9469757519192</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35175,28 +35394,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1538775728620916</v>
+        <v>-0.1492869440294945</v>
       </c>
       <c r="J7" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K7" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06798119415058956</v>
+        <v>0.06481164462620514</v>
       </c>
       <c r="M7" t="n">
-        <v>3.366298672059354</v>
+        <v>3.367376157525376</v>
       </c>
       <c r="N7" t="n">
-        <v>18.68165889496883</v>
+        <v>18.65256790790167</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322228463995029</v>
+        <v>4.318861876455609</v>
       </c>
       <c r="P7" t="n">
-        <v>249.0887986108299</v>
+        <v>249.0401481556381</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35247,28 +35466,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1893983981111089</v>
+        <v>-0.1867766663841857</v>
       </c>
       <c r="J8" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K8" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1239182038788957</v>
+        <v>0.1222440040936098</v>
       </c>
       <c r="M8" t="n">
-        <v>2.986444829699548</v>
+        <v>2.981792676231141</v>
       </c>
       <c r="N8" t="n">
-        <v>14.5945613404194</v>
+        <v>14.5291565432381</v>
       </c>
       <c r="O8" t="n">
-        <v>3.820282887486135</v>
+        <v>3.811713071997694</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7686044574484</v>
+        <v>251.7408280242087</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35319,28 +35538,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2269820386020168</v>
+        <v>-0.2255133783939075</v>
       </c>
       <c r="J9" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K9" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L9" t="n">
-        <v>0.131046096813993</v>
+        <v>0.131141030543663</v>
       </c>
       <c r="M9" t="n">
-        <v>3.496372434132146</v>
+        <v>3.48244481760405</v>
       </c>
       <c r="N9" t="n">
-        <v>19.66004599383251</v>
+        <v>19.54358555711955</v>
       </c>
       <c r="O9" t="n">
-        <v>4.433965042017416</v>
+        <v>4.420812771099852</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8685943089809</v>
+        <v>255.8530308529812</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35391,28 +35610,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1454791084578575</v>
+        <v>-0.1408265429722804</v>
       </c>
       <c r="J10" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K10" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05126046798050032</v>
+        <v>0.04866489820091158</v>
       </c>
       <c r="M10" t="n">
-        <v>3.648688797084351</v>
+        <v>3.646174439635896</v>
       </c>
       <c r="N10" t="n">
-        <v>22.54211125863934</v>
+        <v>22.48721458545324</v>
       </c>
       <c r="O10" t="n">
-        <v>4.747853331626762</v>
+        <v>4.742068597716955</v>
       </c>
       <c r="P10" t="n">
-        <v>256.9371363763867</v>
+        <v>256.8878353701546</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35463,28 +35682,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1286999560756832</v>
+        <v>-0.1258257554658741</v>
       </c>
       <c r="J11" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K11" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04070091030442824</v>
+        <v>0.03945409095562691</v>
       </c>
       <c r="M11" t="n">
-        <v>3.614779944531292</v>
+        <v>3.60581493848449</v>
       </c>
       <c r="N11" t="n">
-        <v>22.46650951028282</v>
+        <v>22.35702970802706</v>
       </c>
       <c r="O11" t="n">
-        <v>4.739884968043299</v>
+        <v>4.728322081672002</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0593722095149</v>
+        <v>256.0289161903635</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35535,28 +35754,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1081509939518085</v>
+        <v>-0.1025898772066578</v>
       </c>
       <c r="J12" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K12" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02641169815999356</v>
+        <v>0.02404370514090692</v>
       </c>
       <c r="M12" t="n">
-        <v>3.978391039617724</v>
+        <v>3.978624352693297</v>
       </c>
       <c r="N12" t="n">
-        <v>24.8124099897751</v>
+        <v>24.77917949624894</v>
       </c>
       <c r="O12" t="n">
-        <v>4.981205676317241</v>
+        <v>4.977868971382126</v>
       </c>
       <c r="P12" t="n">
-        <v>255.7232038641256</v>
+        <v>255.6642809410009</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35607,28 +35826,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2945203375535217</v>
+        <v>-0.2923296581648588</v>
       </c>
       <c r="J13" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K13" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1790938049395427</v>
+        <v>0.1788623920279082</v>
       </c>
       <c r="M13" t="n">
-        <v>3.729198155553606</v>
+        <v>3.716900756768131</v>
       </c>
       <c r="N13" t="n">
-        <v>22.88086536570784</v>
+        <v>22.75577293572927</v>
       </c>
       <c r="O13" t="n">
-        <v>4.783394753280126</v>
+        <v>4.770301136797263</v>
       </c>
       <c r="P13" t="n">
-        <v>261.0544484181558</v>
+        <v>261.0312321767461</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35679,28 +35898,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3760168950703447</v>
+        <v>-0.377014002720571</v>
       </c>
       <c r="J14" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K14" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2573503775518979</v>
+        <v>0.2610641919663969</v>
       </c>
       <c r="M14" t="n">
-        <v>3.814335354086343</v>
+        <v>3.794477050121528</v>
       </c>
       <c r="N14" t="n">
-        <v>23.4802528605717</v>
+        <v>23.33583213410774</v>
       </c>
       <c r="O14" t="n">
-        <v>4.845642667445847</v>
+        <v>4.830717558925148</v>
       </c>
       <c r="P14" t="n">
-        <v>265.2145859032944</v>
+        <v>265.2251434581245</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35751,28 +35970,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4561991419019474</v>
+        <v>-0.4574117903383424</v>
       </c>
       <c r="J15" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K15" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2365077816233082</v>
+        <v>0.2399858340581341</v>
       </c>
       <c r="M15" t="n">
-        <v>5.182661396237111</v>
+        <v>5.159950017498519</v>
       </c>
       <c r="N15" t="n">
-        <v>38.66312961121552</v>
+        <v>38.43259554817119</v>
       </c>
       <c r="O15" t="n">
-        <v>6.217968286443371</v>
+        <v>6.199402838029739</v>
       </c>
       <c r="P15" t="n">
-        <v>267.8906513554518</v>
+        <v>267.9034798184501</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35823,28 +36042,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6192084338141981</v>
+        <v>-0.6262594845388202</v>
       </c>
       <c r="J16" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K16" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3478560979380966</v>
+        <v>0.3551378899093161</v>
       </c>
       <c r="M16" t="n">
-        <v>5.316772642496663</v>
+        <v>5.321980528728012</v>
       </c>
       <c r="N16" t="n">
-        <v>41.36627734685783</v>
+        <v>41.30735698510296</v>
       </c>
       <c r="O16" t="n">
-        <v>6.431662098311588</v>
+        <v>6.427079973448515</v>
       </c>
       <c r="P16" t="n">
-        <v>274.5194137817132</v>
+        <v>274.5941053704564</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35895,28 +36114,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5222748229288303</v>
+        <v>-0.5319361560358447</v>
       </c>
       <c r="J17" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K17" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2445759705933377</v>
+        <v>0.2526355021119039</v>
       </c>
       <c r="M17" t="n">
-        <v>5.435862874207085</v>
+        <v>5.44482933891237</v>
       </c>
       <c r="N17" t="n">
-        <v>48.48463018099947</v>
+        <v>48.55187760889599</v>
       </c>
       <c r="O17" t="n">
-        <v>6.96309056245856</v>
+        <v>6.967917738384688</v>
       </c>
       <c r="P17" t="n">
-        <v>277.5981598513147</v>
+        <v>277.7005181552839</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35967,28 +36186,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3604038119020858</v>
+        <v>-0.3772034592382441</v>
       </c>
       <c r="J18" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K18" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0789601804596215</v>
+        <v>0.08594228915495239</v>
       </c>
       <c r="M18" t="n">
-        <v>7.416464574894154</v>
+        <v>7.459275401001361</v>
       </c>
       <c r="N18" t="n">
-        <v>87.19225759809146</v>
+        <v>87.77421589572029</v>
       </c>
       <c r="O18" t="n">
-        <v>9.337679454665997</v>
+        <v>9.368789457326933</v>
       </c>
       <c r="P18" t="n">
-        <v>280.1868414156245</v>
+        <v>280.3648315559076</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36026,7 +36245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S468"/>
+  <dimension ref="A1:S471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81425,6 +81644,297 @@
         </is>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:35+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-40.729859694208756,172.69704641791273</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-40.72932612192961,172.69640954266424</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-40.72871756153713,172.69588247498103</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-40.72821245036839,172.69555231125392</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-40.727544378511624,172.69519729103308</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-40.726895679656394,172.69488401157534</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-40.726206522544956,172.6946064979747</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-40.72551506432163,172.69433821720983</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>-40.72485973133068,172.69416073793886</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>-40.72415695970022,172.69395018056184</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>-40.7234470394649,172.69378387372194</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>-40.72273651006779,172.69353629318772</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>-40.72203888384192,172.69331085344726</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>-40.72133808241507,172.69309039356983</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>-40.72063660378976,172.69284710722306</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>-40.71992669981622,172.69267545572762</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>-40.71922338103853,172.69246874753605</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-40.729857595254124,172.69704951079066</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-40.729323483264956,172.69641343084749</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-40.72871528067329,172.69588583055975</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-40.72821140929839,172.69555571759264</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-40.72754165978395,172.6952061921627</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-40.726892550391405,172.69489674461687</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-40.726206162544536,172.69460796282428</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-40.72551511971747,172.69433799185543</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>-40.72485899649102,172.69416537488218</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>-40.72415703317112,172.6939497168688</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>-40.72344676365001,172.6937856124704</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>-40.722737176060626,172.69353260663178</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>-40.72203916938469,172.69330923879582</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>-40.721337043248376,172.69309627576544</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>-40.72063556367494,172.69285274567787</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>-40.719927336616145,172.69267200364746</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>-40.71922431414566,172.6924636842626</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-40.72985021892714,172.69706038004594</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-40.72931496757354,172.69642597907307</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-40.72870639730791,172.69589889965368</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-40.72820600244932,172.69557340857602</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-40.727536927182285,172.69522168671995</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-40.726889559588166,172.69490891424837</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>-40.726206605621975,172.69460615993248</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>-40.72551376251911,172.69434351303815</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>-40.72485743495612,172.69417522838637</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>-40.724155802533325,172.6939574837269</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>-40.72344591781749,172.6937909446323</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>-40.722734720211434,172.69354620080642</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>-40.72203702781333,172.69332134868114</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>-40.72133221417565,172.69312361067207</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>-40.720632528236244,172.69286920075925</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>-40.71992644509622,172.69267683655966</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>-40.71922403845493,172.6924651802298</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0574/nzd0574.xlsx
+++ b/data/nzd0574/nzd0574.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S471"/>
+  <dimension ref="A1:S474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30133,6 +30133,195 @@
         <v>256.89</v>
       </c>
       <c r="S471" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="C472" t="n">
+        <v>239.33</v>
+      </c>
+      <c r="D472" t="n">
+        <v>251.05</v>
+      </c>
+      <c r="E472" t="n">
+        <v>248.14</v>
+      </c>
+      <c r="F472" t="n">
+        <v>248.04</v>
+      </c>
+      <c r="G472" t="n">
+        <v>249.64</v>
+      </c>
+      <c r="H472" t="n">
+        <v>249.02</v>
+      </c>
+      <c r="I472" t="n">
+        <v>251.22</v>
+      </c>
+      <c r="J472" t="n">
+        <v>257.82</v>
+      </c>
+      <c r="K472" t="n">
+        <v>255.54</v>
+      </c>
+      <c r="L472" t="n">
+        <v>257.42</v>
+      </c>
+      <c r="M472" t="n">
+        <v>255.95</v>
+      </c>
+      <c r="N472" t="n">
+        <v>254.99</v>
+      </c>
+      <c r="O472" t="n">
+        <v>256.02</v>
+      </c>
+      <c r="P472" t="n">
+        <v>253.75</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>256.18</v>
+      </c>
+      <c r="R472" t="n">
+        <v>257.63</v>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>239.74</v>
+      </c>
+      <c r="C473" t="n">
+        <v>239.27</v>
+      </c>
+      <c r="D473" t="n">
+        <v>250.94</v>
+      </c>
+      <c r="E473" t="n">
+        <v>248.18</v>
+      </c>
+      <c r="F473" t="n">
+        <v>248.46</v>
+      </c>
+      <c r="G473" t="n">
+        <v>249.48</v>
+      </c>
+      <c r="H473" t="n">
+        <v>248.43</v>
+      </c>
+      <c r="I473" t="n">
+        <v>250.97</v>
+      </c>
+      <c r="J473" t="n">
+        <v>257.46</v>
+      </c>
+      <c r="K473" t="n">
+        <v>255.37</v>
+      </c>
+      <c r="L473" t="n">
+        <v>256.53</v>
+      </c>
+      <c r="M473" t="n">
+        <v>255.66</v>
+      </c>
+      <c r="N473" t="n">
+        <v>254.37</v>
+      </c>
+      <c r="O473" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="P473" t="n">
+        <v>253.79</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>256.35</v>
+      </c>
+      <c r="R473" t="n">
+        <v>258</v>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>239.94</v>
+      </c>
+      <c r="C474" t="n">
+        <v>239.07</v>
+      </c>
+      <c r="D474" t="n">
+        <v>250.76</v>
+      </c>
+      <c r="E474" t="n">
+        <v>248.29</v>
+      </c>
+      <c r="F474" t="n">
+        <v>248.15</v>
+      </c>
+      <c r="G474" t="n">
+        <v>249.16</v>
+      </c>
+      <c r="H474" t="n">
+        <v>248.39</v>
+      </c>
+      <c r="I474" t="n">
+        <v>250.76</v>
+      </c>
+      <c r="J474" t="n">
+        <v>256.95</v>
+      </c>
+      <c r="K474" t="n">
+        <v>255.13</v>
+      </c>
+      <c r="L474" t="n">
+        <v>255.96</v>
+      </c>
+      <c r="M474" t="n">
+        <v>255.69</v>
+      </c>
+      <c r="N474" t="n">
+        <v>255.21</v>
+      </c>
+      <c r="O474" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="P474" t="n">
+        <v>255.09</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>259.14</v>
+      </c>
+      <c r="R474" t="n">
+        <v>259.72</v>
+      </c>
+      <c r="S474" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30149,7 +30338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B472"/>
+  <dimension ref="A1:B475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34872,6 +35061,36 @@
       </c>
       <c r="B472" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -35034,28 +35253,28 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1685143509279862</v>
+        <v>0.1712756811408059</v>
       </c>
       <c r="J2" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09013926774685566</v>
+        <v>0.09387672708928374</v>
       </c>
       <c r="M2" t="n">
-        <v>3.294188987100456</v>
+        <v>3.288513823797111</v>
       </c>
       <c r="N2" t="n">
-        <v>16.62584034578931</v>
+        <v>16.55175626207899</v>
       </c>
       <c r="O2" t="n">
-        <v>4.077479656085278</v>
+        <v>4.068384969748929</v>
       </c>
       <c r="P2" t="n">
-        <v>233.0441159231337</v>
+        <v>233.0147425420097</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35106,28 +35325,28 @@
         <v>0.0863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04167293546139676</v>
+        <v>0.04413730844079754</v>
       </c>
       <c r="J3" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K3" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006488507338268223</v>
+        <v>0.007363675676428594</v>
       </c>
       <c r="M3" t="n">
-        <v>3.271123036851405</v>
+        <v>3.264367048541974</v>
       </c>
       <c r="N3" t="n">
-        <v>15.42358060488464</v>
+        <v>15.35078303280847</v>
       </c>
       <c r="O3" t="n">
-        <v>3.927286672103863</v>
+        <v>3.918007533531357</v>
       </c>
       <c r="P3" t="n">
-        <v>236.0852630492197</v>
+        <v>236.0590499239862</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35178,28 +35397,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00307981573271992</v>
+        <v>0.004939591713192483</v>
       </c>
       <c r="J4" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L4" t="n">
-        <v>3.376744924754593e-05</v>
+        <v>8.801599800212223e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.355550523521987</v>
+        <v>3.34423215042842</v>
       </c>
       <c r="N4" t="n">
-        <v>16.29241525654031</v>
+        <v>16.20337910486485</v>
       </c>
       <c r="O4" t="n">
-        <v>4.036386410707022</v>
+        <v>4.02534211028887</v>
       </c>
       <c r="P4" t="n">
-        <v>249.3189346359805</v>
+        <v>249.2991530771002</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35250,28 +35469,28 @@
         <v>0.0901</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03544817071878493</v>
+        <v>-0.03294016830201327</v>
       </c>
       <c r="J5" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004487787316071801</v>
+        <v>0.003926271683796445</v>
       </c>
       <c r="M5" t="n">
-        <v>3.252309521204915</v>
+        <v>3.245178070418723</v>
       </c>
       <c r="N5" t="n">
-        <v>16.16779925049262</v>
+        <v>16.09111341959344</v>
       </c>
       <c r="O5" t="n">
-        <v>4.020920199468353</v>
+        <v>4.011373009281665</v>
       </c>
       <c r="P5" t="n">
-        <v>247.1259489243954</v>
+        <v>247.0992692969937</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35322,28 +35541,28 @@
         <v>0.0813</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08455237795812463</v>
+        <v>-0.0801684484069104</v>
       </c>
       <c r="J6" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02401536293709117</v>
+        <v>0.02184240634472734</v>
       </c>
       <c r="M6" t="n">
-        <v>3.315682856025467</v>
+        <v>3.318456812901633</v>
       </c>
       <c r="N6" t="n">
-        <v>16.85211464782152</v>
+        <v>16.8243632236474</v>
       </c>
       <c r="O6" t="n">
-        <v>4.105132719879045</v>
+        <v>4.101751238635444</v>
       </c>
       <c r="P6" t="n">
-        <v>246.9469757519192</v>
+        <v>246.9003407492374</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35394,28 +35613,28 @@
         <v>0.0902</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1492869440294945</v>
+        <v>-0.1438309729092883</v>
       </c>
       <c r="J7" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K7" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06481164462620514</v>
+        <v>0.06087178239965307</v>
       </c>
       <c r="M7" t="n">
-        <v>3.367376157525376</v>
+        <v>3.37308808829237</v>
       </c>
       <c r="N7" t="n">
-        <v>18.65256790790167</v>
+        <v>18.65679494176522</v>
       </c>
       <c r="O7" t="n">
-        <v>4.318861876455609</v>
+        <v>4.319351217690595</v>
       </c>
       <c r="P7" t="n">
-        <v>249.0401481556381</v>
+        <v>248.9821133981847</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35466,28 +35685,28 @@
         <v>0.0733</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1867766663841857</v>
+        <v>-0.1843890577812888</v>
       </c>
       <c r="J8" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K8" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1222440040936098</v>
+        <v>0.1208287684894102</v>
       </c>
       <c r="M8" t="n">
-        <v>2.981792676231141</v>
+        <v>2.975941039390781</v>
       </c>
       <c r="N8" t="n">
-        <v>14.5291565432381</v>
+        <v>14.46094719810358</v>
       </c>
       <c r="O8" t="n">
-        <v>3.811713071997694</v>
+        <v>3.80275521143599</v>
       </c>
       <c r="P8" t="n">
-        <v>251.7408280242087</v>
+        <v>251.7154341542521</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35538,28 +35757,28 @@
         <v>0.0664</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2255133783939075</v>
+        <v>-0.223981312048478</v>
       </c>
       <c r="J9" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K9" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L9" t="n">
-        <v>0.131141030543663</v>
+        <v>0.1311400252933062</v>
       </c>
       <c r="M9" t="n">
-        <v>3.48244481760405</v>
+        <v>3.469055672879406</v>
       </c>
       <c r="N9" t="n">
-        <v>19.54358555711955</v>
+        <v>19.42949118712969</v>
       </c>
       <c r="O9" t="n">
-        <v>4.420812771099852</v>
+        <v>4.407889652331339</v>
       </c>
       <c r="P9" t="n">
-        <v>255.8530308529812</v>
+        <v>255.8367363633091</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35610,28 +35829,28 @@
         <v>0.0649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1408265429722804</v>
+        <v>-0.1354832641744095</v>
       </c>
       <c r="J10" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K10" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04866489820091158</v>
+        <v>0.04558984960675716</v>
       </c>
       <c r="M10" t="n">
-        <v>3.646174439635896</v>
+        <v>3.646677289642663</v>
       </c>
       <c r="N10" t="n">
-        <v>22.48721458545324</v>
+        <v>22.46267758915383</v>
       </c>
       <c r="O10" t="n">
-        <v>4.742068597716955</v>
+        <v>4.739480729906371</v>
       </c>
       <c r="P10" t="n">
-        <v>256.8878353701546</v>
+        <v>256.8310017080854</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35682,28 +35901,28 @@
         <v>0.0576</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1258257554658741</v>
+        <v>-0.1224680698311065</v>
       </c>
       <c r="J11" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K11" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03945409095562691</v>
+        <v>0.03789088299274301</v>
       </c>
       <c r="M11" t="n">
-        <v>3.60581493848449</v>
+        <v>3.599387129248488</v>
       </c>
       <c r="N11" t="n">
-        <v>22.35702970802706</v>
+        <v>22.2617182084461</v>
       </c>
       <c r="O11" t="n">
-        <v>4.728322081672002</v>
+        <v>4.718232530137328</v>
       </c>
       <c r="P11" t="n">
-        <v>256.0289161903635</v>
+        <v>255.9932014231484</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35754,28 +35973,28 @@
         <v>0.0526</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1025898772066578</v>
+        <v>-0.09797433508260346</v>
       </c>
       <c r="J12" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K12" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02404370514090692</v>
+        <v>0.02220199556605762</v>
       </c>
       <c r="M12" t="n">
-        <v>3.978624352693297</v>
+        <v>3.974566059978789</v>
       </c>
       <c r="N12" t="n">
-        <v>24.77917949624894</v>
+        <v>24.71184181050918</v>
       </c>
       <c r="O12" t="n">
-        <v>4.977868971382126</v>
+        <v>4.971100663888147</v>
       </c>
       <c r="P12" t="n">
-        <v>255.6642809410009</v>
+        <v>255.6151924930427</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35826,28 +36045,28 @@
         <v>0.0537</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2923296581648588</v>
+        <v>-0.289049320566958</v>
       </c>
       <c r="J13" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K13" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1788623920279082</v>
+        <v>0.1773409042896555</v>
       </c>
       <c r="M13" t="n">
-        <v>3.716900756768131</v>
+        <v>3.710521228766967</v>
       </c>
       <c r="N13" t="n">
-        <v>22.75577293572927</v>
+        <v>22.65573841362447</v>
       </c>
       <c r="O13" t="n">
-        <v>4.770301136797263</v>
+        <v>4.759804451195918</v>
       </c>
       <c r="P13" t="n">
-        <v>261.0312321767461</v>
+        <v>260.9963394250478</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35898,28 +36117,28 @@
         <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.377014002720571</v>
+        <v>-0.3771821434351462</v>
       </c>
       <c r="J14" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K14" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2610641919663969</v>
+        <v>0.2639652082431957</v>
       </c>
       <c r="M14" t="n">
-        <v>3.794477050121528</v>
+        <v>3.772123161470016</v>
       </c>
       <c r="N14" t="n">
-        <v>23.33583213410774</v>
+        <v>23.18874441729428</v>
       </c>
       <c r="O14" t="n">
-        <v>4.830717558925148</v>
+        <v>4.815469283184587</v>
       </c>
       <c r="P14" t="n">
-        <v>265.2251434581245</v>
+        <v>265.2269315470704</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35970,28 +36189,28 @@
         <v>0.0466</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4574117903383424</v>
+        <v>-0.4575610499043483</v>
       </c>
       <c r="J15" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K15" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2399858340581341</v>
+        <v>0.2426859826790861</v>
       </c>
       <c r="M15" t="n">
-        <v>5.159950017498519</v>
+        <v>5.130211180607597</v>
       </c>
       <c r="N15" t="n">
-        <v>38.43259554817119</v>
+        <v>38.19027003243667</v>
       </c>
       <c r="O15" t="n">
-        <v>6.199402838029739</v>
+        <v>6.179827670124522</v>
       </c>
       <c r="P15" t="n">
-        <v>267.9034798184501</v>
+        <v>267.9050733213906</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36042,28 +36261,28 @@
         <v>0.0412</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6262594845388202</v>
+        <v>-0.6304275997524331</v>
       </c>
       <c r="J16" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K16" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3551378899093161</v>
+        <v>0.3610220538704851</v>
       </c>
       <c r="M16" t="n">
-        <v>5.321980528728012</v>
+        <v>5.311303167463863</v>
       </c>
       <c r="N16" t="n">
-        <v>41.30735698510296</v>
+        <v>41.11931803608667</v>
       </c>
       <c r="O16" t="n">
-        <v>6.427079973448515</v>
+        <v>6.412434641856919</v>
       </c>
       <c r="P16" t="n">
-        <v>274.5941053704564</v>
+        <v>274.6384358559393</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36114,28 +36333,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5319361560358447</v>
+        <v>-0.5393663003589438</v>
       </c>
       <c r="J17" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K17" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2526355021119039</v>
+        <v>0.2596730564265853</v>
       </c>
       <c r="M17" t="n">
-        <v>5.44482933891237</v>
+        <v>5.444117966484266</v>
       </c>
       <c r="N17" t="n">
-        <v>48.55187760889599</v>
+        <v>48.48279100262874</v>
       </c>
       <c r="O17" t="n">
-        <v>6.967917738384688</v>
+        <v>6.962958494966686</v>
       </c>
       <c r="P17" t="n">
-        <v>277.7005181552839</v>
+        <v>277.7795392526955</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36186,28 +36405,28 @@
         <v>0.0308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3772034592382441</v>
+        <v>-0.3915655734145033</v>
       </c>
       <c r="J18" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K18" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08594228915495239</v>
+        <v>0.09236626977178775</v>
       </c>
       <c r="M18" t="n">
-        <v>7.459275401001361</v>
+        <v>7.489786344298234</v>
       </c>
       <c r="N18" t="n">
-        <v>87.77421589572029</v>
+        <v>88.07031625700154</v>
       </c>
       <c r="O18" t="n">
-        <v>9.368789457326933</v>
+        <v>9.384578640354693</v>
       </c>
       <c r="P18" t="n">
-        <v>280.3648315559076</v>
+        <v>280.5175956553427</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36245,7 +36464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S471"/>
+  <dimension ref="A1:S474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81935,6 +82154,297 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-40.72984871967356,172.69706258924387</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-40.72931448781625,172.6964266860153</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-40.72870627726242,172.69589907626306</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-40.72820559945425,172.69557472715852</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-40.727537262827866,172.69522058781527</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>-40.72688975343655,172.694908125476</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>-40.7262056917747,172.69460987839676</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>-40.72551379021703,172.69434340036096</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>-40.72485673685789,172.6941796334822</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>-40.72415539844318,172.69396003403847</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>-40.72344628557079,172.69378862630109</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>-40.72273384609524,172.69355103941072</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>-40.72203684425,172.69332238667127</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>-40.72133284582688,172.69312003522037</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>-40.72063142443976,172.69287518442482</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>-40.71992585074949,172.69268005850108</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>-40.71922246913817,172.692473695735</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-40.72984967919586,172.69706117535722</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-40.72931484763422,172.6964261558086</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-40.72870693751261,172.69589810491158</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-40.72820546512255,172.695575166686</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-40.72753585311637,172.69522520321493</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-40.72689019651859,172.69490632256768</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>-40.72620732562279,172.69460323023324</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>-40.72551448266521,172.694340583431</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>-40.72485739821411,172.6941754602335</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>-40.72415571069466,172.6939580633432</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>-40.7234479220724,172.69377830972675</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>-40.72273444965168,172.69354769846964</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>-40.72203810879713,172.69331523607244</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>-40.72133512792073,172.69310711745885</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>-40.72063133953234,172.6928756447068</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>-40.71992548989608,172.69268201467975</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>-40.71922168447954,172.69247795348744</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-40.72984847979299,172.69706294271552</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-40.72931604702747,172.6964243884531</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-40.72870801792198,172.69589651542734</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-40.728205095710386,172.6955763753866</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-40.727536893617724,172.69522179661044</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>-40.72689108268256,172.694902716751</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>-40.72620743639214,172.6946027795103</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>-40.72551506432163,172.69433821720983</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>-40.724858335135174,172.69416954813107</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>-40.7241561515202,172.69395528118508</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>-40.723448970168455,172.69377170248225</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>-40.72273438721481,172.69354804408428</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>-40.722036395539625,172.69332492398047</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>-40.72133451664573,172.6931105775736</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>-40.72062858003974,172.69289060386987</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>-40.71991956764999,172.69271411902093</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>-40.71921803687523,172.6924977462813</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
